--- a/Week3_DermaSmart_AI_Audit_Log.xlsx
+++ b/Week3_DermaSmart_AI_Audit_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LEARNING\Semester5\SWP391\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493486DD-0B7A-4C37-9042-081F6A2CAFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E4E786-E373-4437-9258-DB7F21CF54F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>Student ID:</t>
   </si>
   <si>
-    <t>DE190135</t>
-  </si>
-  <si>
     <t>Course:</t>
   </si>
   <si>
@@ -667,6 +664,9 @@
   </si>
   <si>
     <t>Nguyễn Quang Nhựt</t>
+  </si>
+  <si>
+    <t>DE190056</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1247,187 +1247,187 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" s="6">
         <v>3</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="6">
         <v>2</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="6">
         <v>3</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="6">
         <v>2</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1455,7 +1455,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="2" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -1479,340 +1479,340 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="115.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="115.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="115.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="101.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="H7" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="101.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="H9" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="115.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="F10" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="101.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="H11" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="115.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="F12" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="G12" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="H12" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="115.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="H13" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
         <v>121</v>
       </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>122</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>123</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>124</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>125</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>126</v>
-      </c>
-      <c r="H14" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
         <v>128</v>
       </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>129</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>130</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>131</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>132</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>133</v>
-      </c>
-      <c r="H15" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1838,7 +1838,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1848,7 +1848,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -1858,82 +1858,82 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="72.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="F5" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="72.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>156</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -1994,7 +1994,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -2010,218 +2010,218 @@
     </row>
     <row r="4" spans="1:4" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B4" s="21"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>170</v>
-      </c>
       <c r="C7" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>172</v>
-      </c>
       <c r="C8" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D8" s="11"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>174</v>
-      </c>
       <c r="C9" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D9" s="11"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>176</v>
-      </c>
       <c r="C10" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D10" s="11"/>
     </row>
     <row r="12" spans="1:4" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B12" s="13"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>163</v>
-      </c>
       <c r="D13" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="D27" s="17" t="s">
         <v>195</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
